--- a/upload/pytest-temp/test_customer_excel_print_layo0/customer-2.xlsx
+++ b/upload/pytest-temp/test_customer_excel_print_layo0/customer-2.xlsx
@@ -1256,60 +1256,33 @@
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="R17:R19"/>
+  <mergeCells count="26">
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="P17:P19"/>
+    <mergeCell ref="M3:M5"/>
     <mergeCell ref="G10:L10"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="C17:C19"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="R3:R5"/>
-    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="C11:H11"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M17:M19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="O17:O19"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="Q17:Q19"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="C3:C5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B16:Q16"/>
     <mergeCell ref="J3:L3"/>
-    <mergeCell ref="H17:I17"/>
     <mergeCell ref="B1:R1"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="J18:J19"/>
     <mergeCell ref="O3:O5"/>
     <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="G9:L9"/>
     <mergeCell ref="I4:I5"/>
-    <mergeCell ref="G9:L9"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="F3:F5"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="H18:H19"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B15:R15"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="G3:G5"/>
-    <mergeCell ref="G23:L23"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="N17:N19"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
